--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q40_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q40_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005805813961068496</v>
+        <v>0.0002430528338112486</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005805813961068496</v>
+        <v>0.0002430528338112486</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003636845612364089</v>
+        <v>0.0001850851514881691</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0005493178787736087</v>
+        <v>0.0002276424086124112</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005493178787736087</v>
+        <v>0.0002276424086124112</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002667180912868171</v>
+        <v>0.0001594831985257865</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0006695343622011267</v>
+        <v>0.0002800515490158159</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006695343622011267</v>
+        <v>0.0002800515490158159</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003075100804732538</v>
+        <v>0.0001797457683360883</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001042493963308427</v>
+        <v>0.0004449631243300905</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001042493963308427</v>
+        <v>0.0004449631243300905</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000466858862065829</v>
+        <v>0.0002781762909760406</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001593213599561291</v>
+        <v>0.0006807400687365095</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001593213599561291</v>
+        <v>0.0006807400687365095</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0007220021680886785</v>
+        <v>0.0004355863030651619</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.002164110852556059</v>
+        <v>0.0009200817981982171</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002164110852556059</v>
+        <v>0.0009200817981982171</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008944901618025416</v>
+        <v>0.0005516122400446781</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.002902988458632498</v>
+        <v>0.001234618162259797</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002902988458632498</v>
+        <v>0.001234618162259797</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001228664988812151</v>
+        <v>0.0007226299529821719</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00360951355944469</v>
+        <v>0.001538897304741324</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00360951355944469</v>
+        <v>0.001538897304741324</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001539190265319758</v>
+        <v>0.0009032349360447513</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.004090649434441272</v>
+        <v>0.001745658250283113</v>
       </c>
       <c r="C10" t="n">
-        <v>0.004090649434441272</v>
+        <v>0.001745658250283113</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001711847690655445</v>
+        <v>0.001023997295726686</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.004306091627277656</v>
+        <v>0.001836032595226975</v>
       </c>
       <c r="C11" t="n">
-        <v>0.004306091627277656</v>
+        <v>0.001836032595226975</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001775153023272581</v>
+        <v>0.001075934154812484</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.004271055577593158</v>
+        <v>0.001818523384133495</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004271055577593158</v>
+        <v>0.001818523384133495</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001767426152358945</v>
+        <v>0.001071774044515408</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.004122860253864361</v>
+        <v>0.001754363235095897</v>
       </c>
       <c r="C13" t="n">
-        <v>0.004122860253864361</v>
+        <v>0.001754363235095897</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00169842142294974</v>
+        <v>0.001031608620616488</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.003928831211437712</v>
+        <v>0.001672541879119771</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003928831211437712</v>
+        <v>0.001672541879119771</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001606841607670097</v>
+        <v>0.0009806118082834848</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.00366144297160001</v>
+        <v>0.001559374282077155</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00366144297160001</v>
+        <v>0.001559374282077155</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001520059070411309</v>
+        <v>0.0009201629544598639</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00355115700930292</v>
+        <v>0.001513639430124415</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00355115700930292</v>
+        <v>0.001513639430124415</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001463895297194359</v>
+        <v>0.0008887778048241394</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003321552821914454</v>
+        <v>0.001416683879787795</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003321552821914454</v>
+        <v>0.001416683879787795</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001388116683254509</v>
+        <v>0.0008415426785390027</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.003166327569599479</v>
+        <v>0.001351561911370244</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003166327569599479</v>
+        <v>0.001351561911370244</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001336096736386934</v>
+        <v>0.0008083623414302809</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.003209407590183905</v>
+        <v>0.001370611891146051</v>
       </c>
       <c r="C19" t="n">
-        <v>0.003209407590183905</v>
+        <v>0.001370611891146051</v>
       </c>
       <c r="D19" t="n">
-        <v>0.001296335382077826</v>
+        <v>0.0007901764373793808</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.002990099293716116</v>
+        <v>0.001277948779293319</v>
       </c>
       <c r="C20" t="n">
-        <v>0.002990099293716116</v>
+        <v>0.001277948779293319</v>
       </c>
       <c r="D20" t="n">
-        <v>0.001290541967511266</v>
+        <v>0.000773481905868382</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.002895132458810998</v>
+        <v>0.001241507923079645</v>
       </c>
       <c r="C21" t="n">
-        <v>0.002895132458810998</v>
+        <v>0.001241507923079645</v>
       </c>
       <c r="D21" t="n">
-        <v>0.001252626433615085</v>
+        <v>0.0007443180362540033</v>
       </c>
     </row>
   </sheetData>
